--- a/food_beverage_order_forms/014_noodle_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/014_noodle_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stripe_payments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Stripe Payments</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>stripe_payments</t>
+          <t>stripe_gateway</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stripe Payments</t>
+          <t>Stripe Gateway</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>stripe_gateway</t>
+          <t>stripe_payment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stripe Gateway</t>
+          <t>Stripe Payment</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>stripe_payment</t>
+          <t>paypal_payments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stripe Payment</t>
+          <t>PayPal Payments</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>paypal_gateway</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>PayPal Gateway</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>paypal_payments</t>
+          <t>paypal_payment</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PayPal Payments</t>
+          <t>PayPal Payment</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>paypal_gateway</t>
+          <t>authorize.net_payments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PayPal Gateway</t>
+          <t>Authorize.net Payments</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>paypal_payment</t>
+          <t>authorize.net_gateway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PayPal Payment</t>
+          <t>Authorize.net Gateway</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>authorize.net</t>
+          <t>authorize.net_payment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Authorize.net</t>
+          <t>Authorize.net Payment</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>authorize.net_payments</t>
+          <t>square_payments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Authorize.net Payments</t>
+          <t>Square Payments</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>authorize.net_gateway</t>
+          <t>square_gateway</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Authorize.net Gateway</t>
+          <t>Square Gateway</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>authorize.net_payment</t>
+          <t>square_payment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Authorize.net Payment</t>
+          <t>Square Payment</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>braintree_gateway</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Braintree Gateway</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>square_payments</t>
+          <t>braintree_payment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Square Payments</t>
+          <t>Braintree Payment</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>square_gateway</t>
+          <t>first_data_payments</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Square Gateway</t>
+          <t>First Data Payments</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>square_payment</t>
+          <t>first_data_gateway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Square Payment</t>
+          <t>First Data Gateway</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>braintree</t>
+          <t>first_data_payment</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>First Data Payment</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>braintree_payments</t>
+          <t>cybersource_gateway</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Braintree Payments</t>
+          <t>CyberSource Gateway</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>braintree_gateway</t>
+          <t>cybersource_payment</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Braintree Gateway</t>
+          <t>CyberSource Payment</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>braintree_payment</t>
+          <t>worldpay_payments</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Braintree Payment</t>
+          <t>Worldpay Payments</t>
         </is>
       </c>
     </row>
@@ -1740,267 +1740,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>first_data</t>
+          <t>worldpay_gateway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>First Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>first_data_payments</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>First Data Payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>first_data_gateway</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>First Data Gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>first_data_payment</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>First Data Payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>cybersource</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CyberSource</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>cybersource_payments</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CyberSource Payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>cybersource_gateway</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CyberSource Gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>cybersource_payment</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CyberSource Payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>worldpay</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Worldpay</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>worldpay_payments</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Worldpay Payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>worldpay_gateway</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
           <t>Worldpay Gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>worldpay_payment</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Worldpay Payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>bango</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Bango</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>bango_payments</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Bango Payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>bango_gateway</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Bango Gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>bango_payment</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Bango Payment</t>
         </is>
       </c>
     </row>
